--- a/Result/profitability/6233.xlsx
+++ b/Result/profitability/6233.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0225</v>
+        <v>-0.02375</v>
       </c>
       <c r="N2" t="n">
-        <v>39.43</v>
+        <v>39.89</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05375</v>
+        <v>-0.0225</v>
       </c>
       <c r="N3" t="n">
-        <v>40.03999999999999</v>
+        <v>41.11125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03875000000000001</v>
+        <v>0.001249999999999998</v>
       </c>
       <c r="N4" t="n">
-        <v>41.25624999999999</v>
+        <v>42.0525</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01375</v>
+        <v>0.03</v>
       </c>
       <c r="N5" t="n">
-        <v>42.395</v>
+        <v>43.12</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1030,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.005000000000000003</v>
+        <v>0.01875</v>
       </c>
       <c r="N6" t="n">
-        <v>43.14624999999999</v>
+        <v>44.945</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.01125</v>
+        <v>0.03</v>
       </c>
       <c r="N7" t="n">
-        <v>44.845</v>
+        <v>45.48</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0125</v>
+        <v>0.02375</v>
       </c>
       <c r="N8" t="n">
-        <v>45.59625</v>
+        <v>45.935</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>-0.06125</v>
       </c>
       <c r="N12" t="n">
-        <v>48.38250000000001</v>
+        <v>48.3825</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6233</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>108</v>
+      </c>
+      <c r="D75" t="n">
+        <v>58</v>
+      </c>
+      <c r="E75" t="n">
+        <v>50</v>
+      </c>
+      <c r="F75" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>22</v>
+      </c>
+      <c r="J75" t="n">
+        <v>21</v>
+      </c>
+      <c r="K75" t="n">
+        <v>21</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.04500000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>40.265</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-9.666666666666668</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.710000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06247118487782388</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.888888888888889</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.800000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1439563167038969</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
